--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N56_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0001T0006Z000C1N56_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.21877036766759</v>
+        <v>14.33555018474598</v>
       </c>
       <c r="D2" t="n">
-        <v>87.91365654169316</v>
+        <v>14.28596918802514</v>
       </c>
       <c r="E2" t="n">
-        <v>16.09754864596811</v>
+        <v>2.615851654969818</v>
       </c>
       <c r="F2" t="n">
-        <v>15.7066368412681</v>
+        <v>2.552328486706066</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.28955307457156</v>
+        <v>9.14705237461788</v>
       </c>
       <c r="D3" t="n">
-        <v>56.43245950758664</v>
+        <v>9.170274669982829</v>
       </c>
       <c r="E3" t="n">
-        <v>16.09754864596811</v>
+        <v>2.615851654969818</v>
       </c>
       <c r="F3" t="n">
-        <v>15.7066368412681</v>
+        <v>2.552328486706066</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.21710509771336</v>
+        <v>8.485279578378421</v>
       </c>
       <c r="D4" t="n">
-        <v>53.01989486915868</v>
+        <v>8.615732916238285</v>
       </c>
       <c r="E4" t="n">
-        <v>16.09754864596811</v>
+        <v>2.615851654969818</v>
       </c>
       <c r="F4" t="n">
-        <v>15.7066368412681</v>
+        <v>2.552328486706066</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
